--- a/extraction_results/benchmarks.xlsx
+++ b/extraction_results/benchmarks.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2580" yWindow="1740" windowWidth="14745" windowHeight="12870" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15510" yWindow="405" windowWidth="12960" windowHeight="15795" tabRatio="600" firstSheet="2" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen3_8b" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen3_14b" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="llama3.1_8b" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen3.5_4b" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claude-api" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -4463,4 +4464,1018 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Initials</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AOC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HH</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LH</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HH</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RK</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EK</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AH</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LH</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>JM</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>JC</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Total: 50 patients</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>SUM(B2:B51)</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>SUM(C2:C51)</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>SUM(D2:D51)</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>AVERAGE(E2:E51)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>